--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -930,7 +930,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -992,7 +992,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-03-26</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4566,7 +4566,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-07-13</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5177,7 +5177,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
         <v>16274600</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>28502</v>
+        <v>28552</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>16274600</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>28502</v>
+        <v>28552</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2025-07-07</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2024-05-12</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-02-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-07-23</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5744,7 +5744,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2025-03-12</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7008,7 +7008,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7070,7 +7070,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7380,7 +7380,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8372,7 +8372,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2024-11-24</t>
+          <t>2024-11-25</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2025-02-04</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9488,7 +9488,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9860,7 +9860,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10046,7 +10046,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10232,7 +10232,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10480,7 +10480,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10728,7 +10728,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10790,7 +10790,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11038,7 +11038,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11348,7 +11348,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11782,7 +11782,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11906,7 +11906,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12092,7 +12092,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12278,7 +12278,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12402,7 +12402,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12712,7 +12712,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12898,7 +12898,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13270,7 +13270,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13332,7 +13332,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13394,7 +13394,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13580,7 +13580,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13642,7 +13642,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-06-27</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13828,7 +13828,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -14380,7 +14380,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14442,7 +14442,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14566,7 +14566,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14690,7 +14690,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14752,7 +14752,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15000,7 +15000,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15062,7 +15062,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15372,7 +15372,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15434,7 +15434,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15496,7 +15496,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15682,7 +15682,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15744,7 +15744,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15806,7 +15806,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15868,7 +15868,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15930,7 +15930,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-02-17</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16054,7 +16054,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-07-29</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16178,7 +16178,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16426,7 +16426,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16736,7 +16736,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16860,7 +16860,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16922,7 +16922,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17046,7 +17046,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-07-01</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17108,7 +17108,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17170,7 +17170,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17232,7 +17232,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2023-07-31</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17294,7 +17294,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2023-09-18</t>
+          <t>2023-09-19</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17480,7 +17480,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17728,7 +17728,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-05-25</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17852,7 +17852,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18038,7 +18038,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18162,7 +18162,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18348,7 +18348,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18410,7 +18410,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18472,7 +18472,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18534,7 +18534,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18596,7 +18596,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18658,7 +18658,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18720,7 +18720,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2023-07-30</t>
+          <t>2023-07-31</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18782,7 +18782,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18906,7 +18906,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19030,7 +19030,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19092,7 +19092,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19154,7 +19154,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2023-10-19</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19216,7 +19216,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19278,7 +19278,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-06-10</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19472,7 +19472,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19534,7 +19534,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19596,7 +19596,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19658,7 +19658,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-06-09</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19720,7 +19720,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19852,7 +19852,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19914,7 +19914,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19976,7 +19976,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -20038,7 +20038,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20162,7 +20162,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20224,7 +20224,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20286,7 +20286,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20488,7 +20488,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-03-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-02-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20612,7 +20612,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20938,7 +20938,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -21000,7 +21000,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21124,7 +21124,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21186,7 +21186,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21388,7 +21388,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-05-12</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21636,7 +21636,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2023-07-14</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21768,7 +21768,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21892,7 +21892,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21954,7 +21954,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22334,7 +22334,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22396,7 +22396,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22458,7 +22458,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22520,7 +22520,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22714,7 +22714,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22776,7 +22776,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-02-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22838,7 +22838,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22900,7 +22900,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22962,7 +22962,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23218,7 +23218,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23280,7 +23280,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23342,7 +23342,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2023-08-10</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23598,7 +23598,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23660,7 +23660,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23722,7 +23722,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23784,7 +23784,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-08-02</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23846,7 +23846,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -24040,7 +24040,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -24102,7 +24102,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24226,7 +24226,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2023-10-09</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24288,7 +24288,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24482,7 +24482,7 @@
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
@@ -24544,7 +24544,7 @@
       </c>
       <c r="G382" s="3" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-02-11</t>
         </is>
       </c>
       <c r="H382" s="5" t="n">
@@ -24606,7 +24606,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -24668,7 +24668,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -24730,7 +24730,7 @@
       </c>
       <c r="G385" s="3" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H385" s="5" t="n">
@@ -24924,7 +24924,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -24986,7 +24986,7 @@
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
@@ -25048,7 +25048,7 @@
       </c>
       <c r="G390" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H390" s="5" t="n">
@@ -25110,7 +25110,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2023-08-09</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25172,7 +25172,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -25374,7 +25374,7 @@
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H395" s="5" t="n">
@@ -25436,7 +25436,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-02-11</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>2025-06-19</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
@@ -25560,7 +25560,7 @@
       </c>
       <c r="G398" s="3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H398" s="5" t="n">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="G402" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H402" s="5" t="n">
@@ -25886,7 +25886,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -25948,7 +25948,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26010,7 +26010,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2023-08-08</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -26072,7 +26072,7 @@
       </c>
       <c r="G406" s="3" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="H406" s="5" t="n">
@@ -26274,7 +26274,7 @@
       </c>
       <c r="G409" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H409" s="5" t="n">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="G410" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H410" s="5" t="n">
@@ -26398,7 +26398,7 @@
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H411" s="5" t="n">
@@ -26460,7 +26460,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
+          <t>2024-06-03</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -26522,7 +26522,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -26724,7 +26724,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -26786,7 +26786,7 @@
       </c>
       <c r="G417" s="3" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="H417" s="5" t="n">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="G418" s="3" t="inlineStr">
         <is>
-          <t>2025-06-22</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="H418" s="5" t="n">
@@ -26910,7 +26910,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2024-06-04</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -26972,7 +26972,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2025-02-23</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -27236,7 +27236,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -27298,7 +27298,7 @@
       </c>
       <c r="G425" s="3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="H425" s="5" t="n">
@@ -27360,7 +27360,7 @@
       </c>
       <c r="G426" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H426" s="5" t="n">
@@ -27422,7 +27422,7 @@
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H427" s="5" t="n">
@@ -28132,7 +28132,7 @@
           <t>C | 658呎 (3房)
 $2042万
 $31,027/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -28140,7 +28140,7 @@
           <t>D | 616呎 (2房)
 $1817万
 $29,491/呎
-(25年-05月-20日)</t>
+(25年-05月-21日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -28148,7 +28148,7 @@
           <t>E | 570呎 (2房)
 $1725万
 $30,261/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -28156,7 +28156,7 @@
           <t>F | 581呎 (2房)
 $1391万
 $23,946/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -28164,7 +28164,7 @@
           <t>G | 509呎 (2房)
 $1062万
 $20,870/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -28188,7 +28188,7 @@
           <t>C | 658呎 (3房)
 $2010万
 $30,550/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -28196,7 +28196,7 @@
           <t>D | 616呎 (2房)
 $1788万
 $29,028/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -28204,7 +28204,7 @@
           <t>E | 571呎 (2房)
 $1701万
 $29,792/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -28212,7 +28212,7 @@
           <t>F | 582呎 (2房)
 $1289万
 $22,154/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -28220,7 +28220,7 @@
           <t>G | 509呎 (2房)
 $1048万
 $20,580/呎
-(25年-03月-02日)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
     </row>
@@ -28244,7 +28244,7 @@
           <t>C | 658呎 (3房)
 $1999万
 $30,381/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -28252,7 +28252,7 @@
           <t>D | 616呎 (2房)
 $1778万
 $28,857/呎
-(25年-03月-27日)</t>
+(25年-03月-28日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -28260,7 +28260,7 @@
           <t>E | 571呎 (2房)
 $1694万
 $29,674/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -28268,7 +28268,7 @@
           <t>F | 582呎 (2房)
 $1284万
 $22,065/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -28276,7 +28276,7 @@
           <t>G | 509呎 (2房)
 $1043万
 $20,498/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -28291,7 +28291,7 @@
           <t>A | 853呎 (3房)
 $3444万
 $40,375/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -28300,7 +28300,7 @@
           <t>C | 659呎 (3房)
 $1988万
 $30,161/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -28308,7 +28308,7 @@
           <t>D | 616呎 (2房)
 $1766万
 $28,662/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -28316,7 +28316,7 @@
           <t>E | 571呎 (2房)
 $1796万
 $31,450/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -28324,7 +28324,7 @@
           <t>F | 505呎 (2房)
 $1279万
 $25,329/呎
-(25年-07月-10日)</t>
+(25年-07月-11日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -28332,7 +28332,7 @@
           <t>G | 509呎 (2房)
 $1039万
 $20,418/呎
-(25年-02月-27日)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
     </row>
@@ -28356,7 +28356,7 @@
           <t>C | 658呎 (3房)
 $1988万
 $30,207/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -28364,7 +28364,7 @@
           <t>D | 616呎 (2房)
 $1766万
 $28,662/呎
-(25年-03月-26日)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -28372,7 +28372,7 @@
           <t>E | 571呎 (2房)
 $1680万
 $29,425/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -28380,7 +28380,7 @@
           <t>F | 582呎 (2房)
 $1279万
 $21,978/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -28388,7 +28388,7 @@
           <t>G | 509呎 (2房)
 $1039万
 $20,418/呎
-(25年-02月-23日)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
     </row>
@@ -28412,7 +28412,7 @@
           <t>C | 661呎 (3房)
 $2074万
 $31,378/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -28420,7 +28420,7 @@
           <t>D | 613呎 (2房)
 $1715万
 $27,981/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -28428,7 +28428,7 @@
           <t>E | 571呎 (2房)
 $1667万
 $29,193/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -28436,7 +28436,7 @@
           <t>F | 582呎 (2房)
 $1269万
 $21,804/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -28444,7 +28444,7 @@
           <t>G | 509呎 (2房)
 $1031万
 $20,256/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
           <t>A | 853呎 (3房)
 $3246万
 $38,060/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
@@ -28468,7 +28468,7 @@
           <t>C | 661呎 (3房)
 $1948万
 $29,469/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -28476,7 +28476,7 @@
           <t>D | 613呎 (2房)
 $1689万
 $27,561/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -28484,7 +28484,7 @@
           <t>E | 571呎 (2房)
 $1660万
 $29,076/呎
-(25年-12月-02日)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -28492,7 +28492,7 @@
           <t>F | 582呎 (2房)
 $1264万
 $21,715/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -28500,7 +28500,7 @@
           <t>G | 509呎 (2房)
 $1053万
 $20,692/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
     </row>
@@ -28515,7 +28515,7 @@
           <t>A | 853呎 (3房)
 $3030万
 $35,518/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
@@ -28524,7 +28524,7 @@
           <t>C | 661呎 (3房)
 $1889万
 $28,571/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -28532,7 +28532,7 @@
           <t>D | 613呎 (2房)
 $1680万
 $27,399/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -28540,7 +28540,7 @@
           <t>E | 570呎 (2房)
 $1654万
 $29,012/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -28548,7 +28548,7 @@
           <t>F | 582呎 (2房)
 $1259万
 $21,628/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -28556,7 +28556,7 @@
           <t>G | 509呎 (2房)
 $1049万
 $20,608/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -28571,7 +28571,7 @@
           <t>A | 853呎 (3房)
 $3009万
 $35,271/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
@@ -28580,7 +28580,7 @@
           <t>C | 661呎 (3房)
 $1878万
 $28,413/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -28588,7 +28588,7 @@
           <t>D | 613呎 (2房)
 $1670万
 $27,236/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -28596,7 +28596,7 @@
           <t>E | 571呎 (2房)
 $1647万
 $28,845/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -28604,7 +28604,7 @@
           <t>F | 582呎 (2房)
 $1254万
 $21,544/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -28612,7 +28612,7 @@
           <t>G | 509呎 (2房)
 $1019万
 $20,012/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -28627,7 +28627,7 @@
           <t>A | 853呎 (3房)
 $2988万
 $35,026/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
@@ -28636,7 +28636,7 @@
           <t>C | 661呎 (3房)
 $1868万
 $28,254/呎
-(25年-04月-16日)</t>
+(25年-04月-17日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -28644,7 +28644,7 @@
           <t>D | 613呎 (2房)
 $1669万
 $27,228/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -28652,7 +28652,7 @@
           <t>E | 571呎 (2房)
 $1640万
 $28,730/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -28660,7 +28660,7 @@
           <t>F | 582呎 (2房)
 $1249万
 $21,458/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -28668,7 +28668,7 @@
           <t>G | 509呎 (2房)
 $1015万
 $19,934/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28683,7 +28683,7 @@
           <t>A | 853呎 (3房)
 $3182万
 $37,300/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
@@ -28692,7 +28692,7 @@
           <t>C | 661呎 (3房)
 $1857万
 $28,097/呎
-(25年-04月-23日)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -28700,7 +28700,7 @@
           <t>D | 613呎 (2房)
 $1659万
 $27,067/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -28708,7 +28708,7 @@
           <t>E | 570呎 (2房)
 $1634万
 $28,666/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -28716,7 +28716,7 @@
           <t>F | 582呎 (2房)
 $1244万
 $21,372/呎
-(25年-07月-13日)</t>
+(25年-07月-14日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -28724,7 +28724,7 @@
           <t>G | 509呎 (2房)
 $1011万
 $19,854/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -28739,7 +28739,7 @@
           <t>A | 853呎 (3房)
 $3224万
 $37,801/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr"/>
@@ -28748,7 +28748,7 @@
           <t>C | 661呎 (3房)
 $1847万
 $27,940/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -28756,15 +28756,15 @@
           <t>D | 613呎 (2房)
 $1649万
 $26,908/呎
-(25年-02月-26日)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
         <is>
-          <t>E | 571呎 (2房)
+          <t>E | 570呎 (2房)
 $1627万
-$28,502/呎
-(26年-01月-04日)</t>
+$28,552/呎
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -28772,7 +28772,7 @@
           <t>F | 582呎 (2房)
 $1239万
 $21,287/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -28780,7 +28780,7 @@
           <t>G | 509呎 (2房)
 $1007万
 $19,776/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
     </row>
@@ -28795,7 +28795,7 @@
           <t>A | 853呎 (3房)
 $3199万
 $37,501/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
@@ -28804,7 +28804,7 @@
           <t>C | 661呎 (3房)
 $1954万
 $29,565/呎
-(25年-07月-22日)</t>
+(25年-07月-23日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -28812,7 +28812,7 @@
           <t>D | 613呎 (2房)
 $1640万
 $26,749/呎
-(25年-02月-09日)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -28820,7 +28820,7 @@
           <t>E | 571呎 (2房)
 $1651万
 $28,908/呎
-(24年-05月-12日)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -28828,7 +28828,7 @@
           <t>F | 582呎 (2房)
 $1234万
 $21,202/呎
-(25年-07月-06日)</t>
+(25年-07月-07日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -28836,7 +28836,7 @@
           <t>G | 509呎 (2房)
 $1003万
 $19,696/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
     </row>
@@ -28860,7 +28860,7 @@
           <t>C | 661呎 (3房)
 $1837万
 $27,784/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -28868,7 +28868,7 @@
           <t>D | 613呎 (2房)
 $1640万
 $26,749/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -28876,7 +28876,7 @@
           <t>E | 571呎 (2房)
 $1621万
 $28,388/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -28884,7 +28884,7 @@
           <t>F | 582呎 (2房)
 $1234万
 $21,202/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -28892,7 +28892,7 @@
           <t>G | 509呎 (2房)
 $1003万
 $19,696/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -28916,7 +28916,7 @@
           <t>C | 661呎 (3房)
 $1817万
 $27,492/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -28924,7 +28924,7 @@
           <t>D | 613呎 (2房)
 $1622万
 $26,460/呎
-(25年-02月-23日)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -28932,7 +28932,7 @@
           <t>E | 570呎 (2房)
 $1615万
 $28,336/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -28940,7 +28940,7 @@
           <t>F | 582呎 (2房)
 $1303万
 $22,383/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -28948,7 +28948,7 @@
           <t>G | 509呎 (2房)
 $995万
 $19,540/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
     </row>
@@ -28972,7 +28972,7 @@
           <t>C | 661呎 (3房)
 $1807万
 $27,339/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -28980,7 +28980,7 @@
           <t>D | 613呎 (2房)
 $1612万
 $26,305/呎
-(25年-03月-12日)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -28988,7 +28988,7 @@
           <t>E | 570呎 (2房)
 $1609万
 $28,224/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -28996,7 +28996,7 @@
           <t>F | 582呎 (2房)
 $1297万
 $22,293/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -29004,7 +29004,7 @@
           <t>G | 509呎 (2房)
 $991万
 $19,463/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -29019,7 +29019,7 @@
           <t>A | 517呎 (2房)
 $1428万
 $27,615/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -29027,7 +29027,7 @@
           <t>B | 520呎 (2房)
 $1450万
 $27,881/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29035,7 +29035,7 @@
           <t>C | 659呎 (3房)
 $1571万
 $23,840/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -29043,7 +29043,7 @@
           <t>D | 618呎 (2房)
 $1371万
 $22,186/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -29051,7 +29051,7 @@
           <t>E | 568呎 (2房)
 $1540万
 $27,114/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -29059,7 +29059,7 @@
           <t>F | 582呎 (2房)
 $1214万
 $20,867/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="H22" s="24" t="inlineStr">
@@ -29082,7 +29082,7 @@
           <t>A | 517呎 (2房)
 $1356万
 $26,226/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29090,7 +29090,7 @@
           <t>B | 520呎 (2房)
 $1444万
 $27,770/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -29098,7 +29098,7 @@
           <t>C | 659呎 (3房)
 $1560万
 $23,675/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -29106,7 +29106,7 @@
           <t>D | 618呎 (2房)
 $1362万
 $22,043/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -29114,7 +29114,7 @@
           <t>E | 568呎 (2房)
 $1534万
 $27,005/呎
-(23年-08月-03日)</t>
+(23年-08月-04日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -29122,7 +29122,7 @@
           <t>F | 582呎 (2房)
 $1210万
 $20,783/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -29130,7 +29130,7 @@
           <t>G | 403呎 (1房)
 $1080万
 $26,788/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
     </row>
@@ -29145,7 +29145,7 @@
           <t>A | 517呎 (2房)
 $1416万
 $27,395/呎
-(23年-07月-31日)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29153,7 +29153,7 @@
           <t>B | 520呎 (2房)
 $1371万
 $26,372/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -29161,7 +29161,7 @@
           <t>C | 659呎 (3房)
 $1549万
 $23,510/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -29169,7 +29169,7 @@
           <t>D | 618呎 (2房)
 $1353万
 $21,899/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -29177,7 +29177,7 @@
           <t>E | 567呎 (2房)
 $1556万
 $27,439/呎
-(24年-10月-16日)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -29185,7 +29185,7 @@
           <t>F | 582呎 (2房)
 $1205万
 $20,701/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="H24" s="24" t="inlineStr">
@@ -29208,7 +29208,7 @@
           <t>A | 517呎 (2房)
 $1345万
 $26,016/呎
-(23年-07月-30日)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -29216,7 +29216,7 @@
           <t>B | 520呎 (2房)
 $1366万
 $26,267/呎
-(25年-11月-11日)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -29224,7 +29224,7 @@
           <t>C | 659呎 (3房)
 $1539万
 $23,347/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -29232,7 +29232,7 @@
           <t>D | 618呎 (2房)
 $1345万
 $21,758/呎
-(25年-02月-03日)</t>
+(25年-02月-04日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -29240,7 +29240,7 @@
           <t>E | 568呎 (2房)
 $1522万
 $26,790/呎
-(24年-11月-24日)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -29248,7 +29248,7 @@
           <t>F | 582呎 (2房)
 $1200万
 $20,619/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H25" s="24" t="inlineStr">
@@ -29271,7 +29271,7 @@
           <t>A | 517呎 (2房)
 $1340万
 $25,912/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -29279,7 +29279,7 @@
           <t>B | 518呎 (2房)
 $1360万
 $26,264/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -29287,7 +29287,7 @@
           <t>C | 659呎 (3房)
 $1528万
 $23,185/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -29295,7 +29295,7 @@
           <t>D | 618呎 (2房)
 $1336万
 $21,618/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -29303,7 +29303,7 @@
           <t>E | 568呎 (2房)
 $1516万
 $26,683/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -29311,7 +29311,7 @@
           <t>F | 582呎 (2房)
 $1195万
 $20,537/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H26" s="24" t="inlineStr">
@@ -29334,7 +29334,7 @@
           <t>A | 517呎 (2房)
 $1561万
 $30,193/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -29342,7 +29342,7 @@
           <t>B | 520呎 (2房)
 $1360万
 $26,163/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -29350,7 +29350,7 @@
           <t>C | 659呎 (3房)
 $1528万
 $23,185/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -29358,7 +29358,7 @@
           <t>D | 618呎 (2房)
 $1370万
 $22,172/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -29366,7 +29366,7 @@
           <t>E | 568呎 (2房)
 $1516万
 $26,683/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -29374,7 +29374,7 @@
           <t>F | 582呎 (2房)
 $1195万
 $20,537/呎
-(25年-07月-09日)</t>
+(25年-07月-10日)</t>
         </is>
       </c>
       <c r="H27" s="24" t="inlineStr">
@@ -29397,7 +29397,7 @@
           <t>A | 517呎 (2房)
 $1329万
 $25,707/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -29405,7 +29405,7 @@
           <t>B | 520呎 (2房)
 $1350万
 $25,955/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -29413,7 +29413,7 @@
           <t>C | 659呎 (3房)
 $1507万
 $22,865/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -29421,7 +29421,7 @@
           <t>D | 618呎 (2房)
 $1319万
 $21,340/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -29429,7 +29429,7 @@
           <t>E | 568呎 (2房)
 $1504万
 $26,471/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -29437,7 +29437,7 @@
           <t>F | 582呎 (2房)
 $1186万
 $20,375/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H28" s="25" t="inlineStr">
@@ -29460,7 +29460,7 @@
           <t>A | 517呎 (2房)
 $1324万
 $25,604/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -29468,7 +29468,7 @@
           <t>B | 520呎 (2房)
 $1344万
 $25,851/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -29476,7 +29476,7 @@
           <t>C | 659呎 (3房)
 $1496万
 $22,707/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -29484,7 +29484,7 @@
           <t>D | 618呎 (2房)
 $1310万
 $21,203/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -29492,7 +29492,7 @@
           <t>E | 568呎 (2房)
 $1498万
 $26,366/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -29500,7 +29500,7 @@
           <t>F | 582呎 (2房)
 $1181万
 $20,293/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="H29" s="25" t="inlineStr">
@@ -29523,7 +29523,7 @@
           <t>A | 517呎 (2房)
 $1318万
 $25,503/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -29531,7 +29531,7 @@
           <t>B | 520呎 (2房)
 $1339万
 $25,748/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -29539,7 +29539,7 @@
           <t>C | 659呎 (3房)
 $1486万
 $22,549/呎
-(25年-03月-20日)</t>
+(25年-03月-21日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -29547,7 +29547,7 @@
           <t>D | 618呎 (2房)
 $1302万
 $21,065/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -29555,7 +29555,7 @@
           <t>E | 567呎 (2房)
 $1492万
 $26,307/呎
-(25年-12月-14日)</t>
+(25年-12月-15日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -29563,7 +29563,7 @@
           <t>F | 582呎 (2房)
 $1176万
 $20,213/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="H30" s="25" t="inlineStr">
@@ -29586,7 +29586,7 @@
           <t>A | 517呎 (2房)
 $1313万
 $25,399/呎
-(25年-10月-26日)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -29594,7 +29594,7 @@
           <t>B | 520呎 (2房)
 $1334万
 $25,646/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -29602,7 +29602,7 @@
           <t>C | 659呎 (3房)
 $1476万
 $22,392/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -29610,7 +29610,7 @@
           <t>D | 618呎 (2房)
 $1293万
 $20,929/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -29618,7 +29618,7 @@
           <t>E | 568呎 (2房)
 $1486万
 $26,156/呎
-(26年-01月-08日)</t>
+(26年-01月-09日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -29626,7 +29626,7 @@
           <t>F | 582呎 (2房)
 $1172万
 $20,133/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
@@ -29649,7 +29649,7 @@
           <t>A | 517呎 (2房)
 $1308万
 $25,300/呎
-(25年-11月-03日)</t>
+(25年-11月-04日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -29657,7 +29657,7 @@
           <t>B | 520呎 (2房)
 $1328万
 $25,543/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -29665,7 +29665,7 @@
           <t>C | 659呎 (3房)
 $1465万
 $22,237/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -29673,7 +29673,7 @@
           <t>D | 618呎 (2房)
 $1285万
 $20,794/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -29681,7 +29681,7 @@
           <t>E | 568呎 (2房)
 $1480万
 $26,052/呎
-(23年-07月-14日)</t>
+(23年-07月-15日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -29689,7 +29689,7 @@
           <t>F | 582呎 (2房)
 $1167万
 $20,052/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H32" s="24" t="inlineStr">
@@ -29712,7 +29712,7 @@
           <t>A | 517呎 (2房)
 $1303万
 $25,198/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -29720,7 +29720,7 @@
           <t>B | 520呎 (2房)
 $1323万
 $25,442/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -29728,7 +29728,7 @@
           <t>C | 659呎 (3房)
 $1455万
 $22,083/呎
-(25年-04月-10日)</t>
+(25年-04月-11日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -29736,7 +29736,7 @@
           <t>D | 618呎 (2房)
 $1277万
 $20,659/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -29744,7 +29744,7 @@
           <t>E | 568呎 (2房)
 $1474万
 $25,948/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -29752,7 +29752,7 @@
           <t>F | 582呎 (2房)
 $1162万
 $19,972/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="H33" s="24" t="inlineStr">
@@ -29775,7 +29775,7 @@
           <t>A | 517呎 (2房)
 $1298万
 $25,098/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -29783,7 +29783,7 @@
           <t>B | 520呎 (2房)
 $1382万
 $26,576/呎
-(23年-08月-09日)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -29791,7 +29791,7 @@
           <t>C | 659呎 (3房)
 $1445万
 $21,928/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -29799,7 +29799,7 @@
           <t>D | 618呎 (2房)
 $1269万
 $20,526/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -29807,7 +29807,7 @@
           <t>E | 567呎 (2房)
 $1603万
 $28,273/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -29815,7 +29815,7 @@
           <t>F | 582呎 (2房)
 $1158万
 $19,891/呎
-(25年-07月-02日)</t>
+(25年-07月-03日)</t>
         </is>
       </c>
       <c r="H34" s="24" t="inlineStr">
@@ -29838,7 +29838,7 @@
           <t>A | 517呎 (2房)
 $1298万
 $25,098/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -29846,7 +29846,7 @@
           <t>B | 520呎 (2房)
 $1318万
 $25,340/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -29854,7 +29854,7 @@
           <t>C | 659呎 (3房)
 $1445万
 $21,928/呎
-(25年-05月-19日)</t>
+(25年-05月-20日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -29862,7 +29862,7 @@
           <t>D | 618呎 (2房)
 $1269万
 $20,526/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -29870,7 +29870,7 @@
           <t>E | 568呎 (2房)
 $1468万
 $25,845/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -29878,7 +29878,7 @@
           <t>F | 582呎 (2房)
 $1158万
 $19,891/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
@@ -29901,7 +29901,7 @@
           <t>A | 517呎 (2房)
 $1287万
 $24,898/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -29909,7 +29909,7 @@
           <t>B | 520呎 (2房)
 $1371万
 $26,364/呎
-(23年-08月-06日)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -29917,7 +29917,7 @@
           <t>C | 659呎 (3房)
 $1425万
 $21,625/呎
-(25年-04月-06日)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -29925,7 +29925,7 @@
           <t>D | 618呎 (2房)
 $1284万
 $20,782/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -29933,7 +29933,7 @@
           <t>E | 567呎 (2房)
 $1590万
 $28,049/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -29941,7 +29941,7 @@
           <t>F | 581呎 (2房)
 $1148万
 $19,767/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="H36" s="24" t="inlineStr">
@@ -29964,7 +29964,7 @@
           <t>A | 517呎 (2房)
 $1282万
 $24,800/呎
-(25年-12月-17日)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -29972,7 +29972,7 @@
           <t>B | 520呎 (2房)
 $1302万
 $25,038/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -29980,7 +29980,7 @@
           <t>C | 659呎 (3房)
 $1415万
 $21,474/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -29988,7 +29988,7 @@
           <t>D | 618呎 (2房)
 $1244万
 $20,132/呎
-(25年-02月-13日)</t>
+(25年-02月-14日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -29996,7 +29996,7 @@
           <t>E | 568呎 (2房)
 $1451万
 $25,538/呎
-(26年-01月-07日)</t>
+(26年-01月-08日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -30004,7 +30004,7 @@
           <t>F | 582呎 (2房)
 $1144万
 $19,654/呎
-(25年-06月-26日)</t>
+(25年-06月-27日)</t>
         </is>
       </c>
       <c r="H37" s="24" t="inlineStr">
@@ -30245,7 +30245,7 @@
           <t>A | 915呎 (3房)
 $3653万
 $39,919/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -30253,7 +30253,7 @@
           <t>B | 678呎 (2房)
 $2219万
 $32,722/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -30261,7 +30261,7 @@
           <t>C | 861呎 (3房)
 $3547万
 $41,201/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -30269,7 +30269,7 @@
           <t>D | 535呎 (2房)
 $1231万
 $23,014/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -30277,7 +30277,7 @@
           <t>E | 486呎 (2房)
 $1092万
 $22,468/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -30285,7 +30285,7 @@
           <t>F | 505呎 (2房)
 $1119万
 $22,160/呎
-(25年-06月-16日)</t>
+(25年-06月-17日)</t>
         </is>
       </c>
       <c r="H6" s="21" t="inlineStr"/>
@@ -30301,7 +30301,7 @@
           <t>A | 915呎 (3房)
 $3561万
 $38,919/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -30309,7 +30309,7 @@
           <t>B | 678呎 (2房)
 $2182万
 $32,176/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -30317,7 +30317,7 @@
           <t>C | 861呎 (3房)
 $3033万
 $35,226/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -30325,7 +30325,7 @@
           <t>D | 535呎 (2房)
 $1214万
 $22,696/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -30333,7 +30333,7 @@
           <t>E | 485呎 (2房)
 $1077万
 $22,202/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -30341,7 +30341,7 @@
           <t>F | 505呎 (2房)
 $1104万
 $21,852/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr"/>
@@ -30357,7 +30357,7 @@
           <t>A | 915呎 (3房)
 $3470万
 $37,919/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -30365,7 +30365,7 @@
           <t>B | 678呎 (2房)
 $2166万
 $31,951/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -30373,7 +30373,7 @@
           <t>C | 861呎 (3房)
 $3010万
 $34,965/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -30381,7 +30381,7 @@
           <t>D | 535呎 (2房)
 $1209万
 $22,605/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -30389,7 +30389,7 @@
           <t>E | 486呎 (2房)
 $1073万
 $22,070/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -30397,7 +30397,7 @@
           <t>F | 505呎 (2房)
 $1099万
 $21,764/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr"/>
@@ -30413,7 +30413,7 @@
           <t>A | 915呎 (3房)
 $3378万
 $36,919/呎
-(25年-07月-21日)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -30421,7 +30421,7 @@
           <t>B | 678呎 (2房)
 $2151万
 $31,729/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -30429,7 +30429,7 @@
           <t>C | 861呎 (3房)
 $2869万
 $33,321/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -30437,7 +30437,7 @@
           <t>D | 535呎 (2房)
 $1205万
 $22,515/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -30445,7 +30445,7 @@
           <t>E | 486呎 (2房)
 $1068万
 $21,980/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -30453,7 +30453,7 @@
           <t>F | 505呎 (2房)
 $1095万
 $21,678/呎
-(25年-06月-05日)</t>
+(25年-06月-06日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr"/>
@@ -30469,7 +30469,7 @@
           <t>A | 915呎 (3房)
 $3378万
 $36,919/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -30477,7 +30477,7 @@
           <t>B | 678呎 (2房)
 $2151万
 $31,729/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -30485,7 +30485,7 @@
           <t>C | 861呎 (3房)
 $2869万
 $33,321/呎
-(25年-07月-29日)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -30493,7 +30493,7 @@
           <t>D | 535呎 (2房)
 $1205万
 $22,515/呎
-(25年-02月-17日)</t>
+(25年-02月-18日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -30501,7 +30501,7 @@
           <t>E | 486呎 (2房)
 $1068万
 $21,980/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -30509,7 +30509,7 @@
           <t>F | 505呎 (2房)
 $1095万
 $21,678/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr"/>
@@ -30525,7 +30525,7 @@
           <t>A | 915呎 (3房)
 $3295万
 $36,011/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30533,7 +30533,7 @@
           <t>B | 678呎 (2房)
 $2122万
 $31,291/呎
-(25年-03月-30日)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -30541,7 +30541,7 @@
           <t>C | 861呎 (3房)
 $2923万
 $33,951/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -30549,7 +30549,7 @@
           <t>D | 535呎 (2房)
 $1195万
 $22,337/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -30557,7 +30557,7 @@
           <t>E | 486呎 (2房)
 $1060万
 $21,805/呎
-(25年-06月-23日)</t>
+(25年-06月-24日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -30565,7 +30565,7 @@
           <t>F | 505呎 (2房)
 $1086万
 $21,507/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr"/>
@@ -30581,7 +30581,7 @@
           <t>A | 915呎 (3房)
 $3411万
 $37,279/呎
-(23年-12月-20日)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30589,7 +30589,7 @@
           <t>B | 678呎 (2房)
 $2138万
 $31,538/呎
-(23年-08月-06日)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -30597,7 +30597,7 @@
           <t>C | 861呎 (3房)
 $2843万
 $33,021/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -30605,7 +30605,7 @@
           <t>D | 535呎 (2房)
 $1190万
 $22,248/呎
-(25年-02月-13日)</t>
+(25年-02月-14日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -30613,7 +30613,7 @@
           <t>E | 485呎 (2房)
 $1056万
 $21,763/呎
-(25年-03月-06日)</t>
+(25年-03月-07日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -30621,7 +30621,7 @@
           <t>F | 505呎 (2房)
 $1082万
 $21,422/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr"/>
@@ -30637,7 +30637,7 @@
           <t>A | 915呎 (3房)
 $3388万
 $37,027/呎
-(23年-09月-18日)</t>
+(23年-09月-19日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -30645,7 +30645,7 @@
           <t>B | 678呎 (2房)
 $2085万
 $30,757/呎
-(23年-07月-31日)</t>
+(23年-08月-01日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -30653,7 +30653,7 @@
           <t>C | 861呎 (3房)
 $2883万
 $33,482/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -30661,7 +30661,7 @@
           <t>D | 535呎 (2房)
 $1186万
 $22,161/呎
-(25年-03月-19日)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -30669,7 +30669,7 @@
           <t>E | 486呎 (2房)
 $1051万
 $21,633/呎
-(25年-07月-01日)</t>
+(25年-07月-02日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -30677,7 +30677,7 @@
           <t>F | 505呎 (2房)
 $1077万
 $21,335/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr"/>
@@ -30693,7 +30693,7 @@
           <t>A | 915呎 (3房)
 $3180万
 $34,754/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -30701,7 +30701,7 @@
           <t>B | 678呎 (2房)
 $2071万
 $30,543/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -30709,7 +30709,7 @@
           <t>C | 861呎 (3房)
 $2863万
 $33,249/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -30717,7 +30717,7 @@
           <t>D | 535呎 (2房)
 $1181万
 $22,072/呎
-(25年-03月-17日)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -30725,7 +30725,7 @@
           <t>E | 486呎 (2房)
 $1047万
 $21,546/呎
-(25年-06月-17日)</t>
+(25年-06月-18日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -30733,7 +30733,7 @@
           <t>F | 505呎 (2房)
 $1073万
 $21,250/呎
-(25年-06月-11日)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr"/>
@@ -30749,7 +30749,7 @@
           <t>A | 915呎 (3房)
 $3157万
 $34,503/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30757,7 +30757,7 @@
           <t>B | 678呎 (2房)
 $2056万
 $30,332/呎
-(23年-07月-14日)</t>
+(23年-07月-15日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -30765,7 +30765,7 @@
           <t>C | 861呎 (3房)
 $2843万
 $33,017/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -30773,7 +30773,7 @@
           <t>D | 535呎 (2房)
 $1176万
 $21,984/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -30781,7 +30781,7 @@
           <t>E | 486呎 (2房)
 $1043万
 $21,461/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -30789,7 +30789,7 @@
           <t>F | 505呎 (2房)
 $1069万
 $21,164/呎
-(25年-05月-25日)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr"/>
@@ -30805,7 +30805,7 @@
           <t>A | 915呎 (3房)
 $3134万
 $34,251/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -30813,7 +30813,7 @@
           <t>B | 678呎 (2房)
 $2042万
 $30,121/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -30821,7 +30821,7 @@
           <t>C | 861呎 (3房)
 $2998万
 $34,816/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -30829,7 +30829,7 @@
           <t>D | 535呎 (2房)
 $1171万
 $21,896/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -30837,7 +30837,7 @@
           <t>E | 486呎 (2房)
 $1039万
 $21,375/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -30845,7 +30845,7 @@
           <t>F | 505呎 (2房)
 $1065万
 $21,080/呎
-(25年-06月-18日)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr"/>
@@ -30861,7 +30861,7 @@
           <t>A | 915呎 (3房)
 $3111万
 $34,000/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -30869,7 +30869,7 @@
           <t>B | 678呎 (2房)
 $2127万
 $31,372/呎
-(23年-07月-30日)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -30877,7 +30877,7 @@
           <t>C | 861呎 (3房)
 $3080万
 $35,776/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -30885,7 +30885,7 @@
           <t>D | 535呎 (2房)
 $1167万
 $21,810/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -30893,7 +30893,7 @@
           <t>E | 486呎 (2房)
 $1035万
 $21,290/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -30901,7 +30901,7 @@
           <t>F | 505呎 (2房)
 $1060万
 $20,997/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr"/>
@@ -30917,7 +30917,7 @@
           <t>A | 915呎 (3房)
 $3088万
 $33,749/呎
-(23年-10月-19日)</t>
+(23年-10月-20日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -30925,7 +30925,7 @@
           <t>B | 678呎 (2房)
 $2051万
 $30,249/呎
-(23年-08月-15日)</t>
+(23年-08月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -30933,7 +30933,7 @@
           <t>C | 861呎 (3房)
 $3059万
 $35,533/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -30941,7 +30941,7 @@
           <t>D | 535呎 (2房)
 $1162万
 $21,722/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -30949,7 +30949,7 @@
           <t>E | 486呎 (2房)
 $1031万
 $21,205/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -30957,7 +30957,7 @@
           <t>F | 505呎 (2房)
 $1056万
 $20,913/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr"/>
@@ -30973,7 +30973,7 @@
           <t>A | 915呎 (3房)
 $3065万
 $33,497/呎
-(25年-06月-12日)</t>
+(25年-06月-13日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -30981,7 +30981,7 @@
           <t>B | 678呎 (2房)
 $1994万
 $29,410/呎
-(23年-08月-10日)</t>
+(23年-08月-11日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -30997,7 +30997,7 @@
           <t>D | 535呎 (2房)
 $1162万
 $21,722/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -31005,7 +31005,7 @@
           <t>E | 486呎 (2房)
 $1031万
 $21,205/呎
-(25年-06月-10日)</t>
+(25年-06月-11日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -31013,7 +31013,7 @@
           <t>F | 505呎 (2房)
 $1056万
 $20,913/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr"/>
@@ -31029,7 +31029,7 @@
           <t>A | 915呎 (3房)
 $3088万
 $33,746/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -31037,7 +31037,7 @@
           <t>B | 678呎 (2房)
 $1942万
 $28,641/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -31053,7 +31053,7 @@
           <t>D | 535呎 (2房)
 $1153万
 $21,550/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -31061,7 +31061,7 @@
           <t>E | 486呎 (2房)
 $1022万
 $21,036/呎
-(25年-06月-08日)</t>
+(25年-06月-09日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -31069,7 +31069,7 @@
           <t>F | 505呎 (2房)
 $1048万
 $20,748/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr"/>
@@ -31085,7 +31085,7 @@
           <t>A | 915呎 (3房)
 $3065万
 $33,495/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -31093,7 +31093,7 @@
           <t>B | 678呎 (2房)
 $1904万
 $28,080/呎
-(25年-04月-09日)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -31101,7 +31101,7 @@
           <t>C | 861呎 (3房)
 $3014万
 $35,000/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -31109,7 +31109,7 @@
           <t>D | 535呎 (2房)
 $1148万
 $21,464/呎
-(25年-03月-18日)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -31117,7 +31117,7 @@
           <t>E | 486呎 (2房)
 $1018万
 $20,951/呎
-(25年-04月-27日)</t>
+(25年-04月-28日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -31125,7 +31125,7 @@
           <t>F | 505呎 (2房)
 $1044万
 $20,665/呎
-(25年-04月-07日)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr"/>
@@ -31141,7 +31141,7 @@
           <t>A | 914呎 (3房)
 $3027万
 $33,120/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -31149,7 +31149,7 @@
           <t>B | 680呎 (2房)
 $1882万
 $27,681/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -31157,7 +31157,7 @@
           <t>C | 629呎 (2房)
 $1452万
 $23,086/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -31165,7 +31165,7 @@
           <t>D | 535呎 (2房)
 $1144万
 $21,376/呎
-(25年-02月-25日)</t>
+(25年-02月-26日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -31173,7 +31173,7 @@
           <t>E | 488呎 (2房)
 $1014万
 $20,782/呎
-(25年-03月-16日)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -31204,7 +31204,7 @@
           <t>A | 914呎 (3房)
 $3044万
 $33,299/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -31212,7 +31212,7 @@
           <t>B | 680呎 (2房)
 $1907万
 $28,048/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -31220,7 +31220,7 @@
           <t>C | 629呎 (2房)
 $1445万
 $22,971/呎
-(25年-03月-31日)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -31228,7 +31228,7 @@
           <t>D | 535呎 (2房)
 $1139万
 $21,292/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -31236,7 +31236,7 @@
           <t>E | 488呎 (2房)
 $1010万
 $20,700/呎
-(25年-03月-02日)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -31267,7 +31267,7 @@
           <t>A | 914呎 (3房)
 $3075万
 $33,639/呎
-(23年-07月-14日)</t>
+(23年-07月-15日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -31275,7 +31275,7 @@
           <t>B | 680呎 (2房)
 $1955万
 $28,743/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -31283,7 +31283,7 @@
           <t>C | 629呎 (2房)
 $1438万
 $22,856/呎
-(25年-05月-11日)</t>
+(25年-05月-12日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -31291,7 +31291,7 @@
           <t>D | 535呎 (2房)
 $1135万
 $21,207/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -31299,7 +31299,7 @@
           <t>E | 488呎 (2房)
 $1006万
 $20,616/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -31330,7 +31330,7 @@
           <t>A | 914呎 (3房)
 $3053万
 $33,405/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -31338,7 +31338,7 @@
           <t>B | 680呎 (2房)
 $1854万
 $27,270/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -31346,7 +31346,7 @@
           <t>C | 629呎 (2房)
 $1431万
 $22,743/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -31354,7 +31354,7 @@
           <t>D | 535呎 (2房)
 $1130万
 $21,123/呎
-(25年-02月-18日)</t>
+(25年-02月-19日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -31362,7 +31362,7 @@
           <t>E | 488呎 (2房)
 $1002万
 $20,536/呎
-(25年-03月-03日)</t>
+(25年-03月-04日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -31370,7 +31370,7 @@
           <t>F | 394呎 (1房)
 $1056万
 $26,810/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -31393,7 +31393,7 @@
           <t>A | 914呎 (3房)
 $2891万
 $31,630/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -31401,7 +31401,7 @@
           <t>B | 680呎 (2房)
 $1879万
 $27,630/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -31409,7 +31409,7 @@
           <t>C | 629呎 (2房)
 $1423万
 $22,629/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -31417,7 +31417,7 @@
           <t>D | 535呎 (2房)
 $1126万
 $21,038/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -31425,7 +31425,7 @@
           <t>E | 488呎 (2房)
 $998万
 $20,453/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="G26" s="24" t="inlineStr">
@@ -31456,7 +31456,7 @@
           <t>A | 914呎 (3房)
 $2891万
 $31,630/呎
-(23年-08月-03日)</t>
+(23年-08月-04日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -31464,7 +31464,7 @@
           <t>B | 680呎 (2房)
 $1845万
 $27,134/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -31472,7 +31472,7 @@
           <t>C | 629呎 (2房)
 $1423万
 $22,629/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -31480,7 +31480,7 @@
           <t>D | 535呎 (2房)
 $1126万
 $21,038/呎
-(25年-02月-04日)</t>
+(25年-02月-05日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -31488,7 +31488,7 @@
           <t>E | 488呎 (2房)
 $998万
 $20,453/呎
-(25年-02月-24日)</t>
+(25年-02月-25日)</t>
         </is>
       </c>
       <c r="G27" s="24" t="inlineStr">
@@ -31519,7 +31519,7 @@
           <t>A | 914呎 (3房)
 $2903万
 $31,764/呎
-(23年-08月-10日)</t>
+(23年-08月-11日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -31527,7 +31527,7 @@
           <t>B | 680呎 (2房)
 $1827万
 $26,865/呎
-(23年-08月-10日)</t>
+(23年-08月-11日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -31535,7 +31535,7 @@
           <t>C | 629呎 (2房)
 $1409万
 $22,406/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -31543,7 +31543,7 @@
           <t>D | 535呎 (2房)
 $1117万
 $20,872/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -31551,7 +31551,7 @@
           <t>E | 488呎 (2房)
 $990万
 $20,293/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="G28" s="24" t="inlineStr">
@@ -31582,7 +31582,7 @@
           <t>A | 914呎 (3房)
 $2883万
 $31,544/呎
-(23年-08月-06日)</t>
+(23年-08月-07日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -31590,7 +31590,7 @@
           <t>B | 680呎 (2房)
 $1818万
 $26,731/呎
-(23年-08月-01日)</t>
+(23年-08月-02日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -31598,7 +31598,7 @@
           <t>C | 629呎 (2房)
 $1402万
 $22,294/呎
-(25年-05月-18日)</t>
+(25年-05月-19日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -31606,7 +31606,7 @@
           <t>D | 535呎 (2房)
 $1112万
 $20,789/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -31614,7 +31614,7 @@
           <t>E | 488呎 (2房)
 $986万
 $20,210/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="G29" s="24" t="inlineStr">
@@ -31645,7 +31645,7 @@
           <t>A | 914呎 (3房)
 $3288万
 $35,974/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -31653,7 +31653,7 @@
           <t>B | 680呎 (2房)
 $1897万
 $27,896/呎
-(23年-10月-09日)</t>
+(23年-10月-10日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -31661,7 +31661,7 @@
           <t>C | 629呎 (2房)
 $1395万
 $22,184/呎
-(25年-04月-28日)</t>
+(25年-04月-29日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -31669,7 +31669,7 @@
           <t>D | 535呎 (2房)
 $1108万
 $20,706/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -31677,7 +31677,7 @@
           <t>E | 488呎 (2房)
 $982万
 $20,130/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="G30" s="24" t="inlineStr">
@@ -31708,7 +31708,7 @@
           <t>A | 914呎 (3房)
 $2928万
 $32,037/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -31716,7 +31716,7 @@
           <t>B | 680呎 (2房)
 $1888万
 $27,758/呎
-(23年-08月-02日)</t>
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -31724,7 +31724,7 @@
           <t>C | 629呎 (2房)
 $1388万
 $22,073/呎
-(25年-05月-27日)</t>
+(25年-05月-28日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -31732,7 +31732,7 @@
           <t>D | 535呎 (2房)
 $1103万
 $20,624/呎
-(25年-02月-10日)</t>
+(25年-02月-11日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -31740,7 +31740,7 @@
           <t>E | 488呎 (2房)
 $978万
 $20,047/呎
-(25年-02月-23日)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
@@ -31771,7 +31771,7 @@
           <t>A | 914呎 (3房)
 $2908万
 $31,815/呎
-(23年-08月-03日)</t>
+(23年-08月-04日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -31779,7 +31779,7 @@
           <t>B | 680呎 (2房)
 $1878万
 $27,620/呎
-(23年-08月-09日)</t>
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -31787,7 +31787,7 @@
           <t>C | 629呎 (2房)
 $1381万
 $21,963/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -31795,7 +31795,7 @@
           <t>D | 535呎 (2房)
 $1099万
 $20,541/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -31803,7 +31803,7 @@
           <t>E | 488呎 (2房)
 $974万
 $19,968/呎
-(25年-03月-10日)</t>
+(25年-03月-11日)</t>
         </is>
       </c>
       <c r="G32" s="24" t="inlineStr">
@@ -31834,7 +31834,7 @@
           <t>A | 914呎 (3房)
 $2753万
 $30,124/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -31842,7 +31842,7 @@
           <t>B | 680呎 (2房)
 $1782万
 $26,204/呎
-(25年-11月-18日)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -31850,7 +31850,7 @@
           <t>C | 629呎 (2房)
 $1375万
 $21,854/呎
-(25年-06月-19日)</t>
+(25年-06月-20日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -31858,7 +31858,7 @@
           <t>D | 535呎 (2房)
 $1094万
 $20,458/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -31866,7 +31866,7 @@
           <t>E | 488呎 (2房)
 $971万
 $19,890/呎
-(25年-02月-11日)</t>
+(25年-02月-12日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -31897,7 +31897,7 @@
           <t>A | 914呎 (3房)
 $2868万
 $31,374/呎
-(23年-08月-08日)</t>
+(23年-08月-09日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -31905,7 +31905,7 @@
           <t>B | 680呎 (2房)
 $1860万
 $27,346/呎
-(23年-08月-07日)</t>
+(23年-08月-08日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -31913,7 +31913,7 @@
           <t>C | 629呎 (2房)
 $1368万
 $21,746/呎
-(25年-04月-02日)</t>
+(25年-04月-03日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -31921,7 +31921,7 @@
           <t>D | 535呎 (2房)
 $1090万
 $20,378/呎
-(25年-02月-05日)</t>
+(25年-02月-06日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -31929,7 +31929,7 @@
           <t>E | 488呎 (2房)
 $967万
 $19,810/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -31960,7 +31960,7 @@
           <t>A | 914呎 (3房)
 $2762万
 $30,216/呎
-(25年-12月-29日)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -31968,7 +31968,7 @@
           <t>B | 680呎 (2房)
 $1805万
 $26,551/呎
-(24年-06月-02日)</t>
+(24年-06月-03日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -31976,7 +31976,7 @@
           <t>C | 629呎 (2房)
 $1368万
 $21,746/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -31984,7 +31984,7 @@
           <t>D | 535呎 (2房)
 $1090万
 $20,378/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -31992,7 +31992,7 @@
           <t>E | 488呎 (2房)
 $967万
 $19,810/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -32023,7 +32023,7 @@
           <t>A | 914呎 (3房)
 $2762万
 $30,216/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -32031,7 +32031,7 @@
           <t>B | 680呎 (2房)
 $1788万
 $26,288/呎
-(24年-06月-04日)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -32039,7 +32039,7 @@
           <t>C | 629呎 (2房)
 $1354万
 $21,530/呎
-(25年-06月-22日)</t>
+(25年-06月-23日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -32047,7 +32047,7 @@
           <t>D | 535呎 (2房)
 $1082万
 $20,216/呎
-(25年-02月-06日)</t>
+(25年-02月-07日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -32055,7 +32055,7 @@
           <t>E | 488呎 (2房)
 $959万
 $19,652/呎
-(25年-02月-13日)</t>
+(25年-02月-14日)</t>
         </is>
       </c>
       <c r="G36" s="20" t="inlineStr">
@@ -32086,7 +32086,7 @@
           <t>A | 914呎 (3房)
 $2678万
 $29,298/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -32094,7 +32094,7 @@
           <t>B | 680呎 (2房)
 $1747万
 $25,688/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -32102,7 +32102,7 @@
           <t>C | 629呎 (2房)
 $1347万
 $21,422/呎
-(25年-06月-24日)</t>
+(25年-06月-25日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -32110,7 +32110,7 @@
           <t>D | 535呎 (2房)
 $1077万
 $20,136/呎
-(25年-02月-12日)</t>
+(25年-02月-13日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -32118,7 +32118,7 @@
           <t>E | 488呎 (2房)
 $955万
 $19,574/呎
-(25年-02月-23日)</t>
+(25年-02月-24日)</t>
         </is>
       </c>
       <c r="G37" s="20" t="inlineStr">

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -2681,7 +2681,7 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -2697,7 +2697,7 @@
         <v>19876000</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>30207</v>
+        <v>30161</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>19876000</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>30207</v>
+        <v>30161</v>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
@@ -11410,14 +11410,14 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-08-10</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
-        <v>14797800</v>
+        <v>15519600</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>26052</v>
+        <v>27323</v>
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
@@ -11425,10 +11425,10 @@
         </is>
       </c>
       <c r="K173" s="5" t="n">
-        <v>14797800</v>
+        <v>15519600</v>
       </c>
       <c r="L173" s="5" t="n">
-        <v>26052</v>
+        <v>27323</v>
       </c>
       <c r="M173" s="3" t="inlineStr">
         <is>
@@ -17976,14 +17976,14 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
-        <v>20564800</v>
+        <v>20941000</v>
       </c>
       <c r="I278" s="5" t="n">
-        <v>30332</v>
+        <v>30886</v>
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
@@ -17991,10 +17991,10 @@
         </is>
       </c>
       <c r="K278" s="5" t="n">
-        <v>20564800</v>
+        <v>20941000</v>
       </c>
       <c r="L278" s="5" t="n">
-        <v>30332</v>
+        <v>30886</v>
       </c>
       <c r="M278" s="3" t="inlineStr">
         <is>
@@ -21636,14 +21636,14 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
-        <v>30745900</v>
+        <v>29315900</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>33639</v>
+        <v>32074</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -21651,10 +21651,10 @@
         </is>
       </c>
       <c r="K336" s="5" t="n">
-        <v>30745900</v>
+        <v>29315900</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>33639</v>
+        <v>32074</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -28353,9 +28353,9 @@
       <c r="C10" s="21" t="inlineStr"/>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>C | 658呎 (3房)
+          <t>C | 659呎 (3房)
 $1988万
-$30,207/呎
+$30,161/呎
 (25年-07月-29日)</t>
         </is>
       </c>
@@ -29679,9 +29679,9 @@
       <c r="F32" s="22" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
-$1480万
-$26,052/呎
-(23年-07月-15日)</t>
+$1552万
+$27,323/呎
+(23年-08月-10日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -30755,9 +30755,9 @@
       <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
-$2056万
-$30,332/呎
-(23年-07月-15日)</t>
+$2094万
+$30,886/呎
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -31265,9 +31265,9 @@
       <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
-$3075万
-$33,639/呎
-(23年-07月-15日)</t>
+$2932万
+$32,074/呎
+(23年-08月-03日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -122,13 +122,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
@@ -284,10 +284,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1245,12 +1245,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1640,12 +1640,12 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2005,12 +2005,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -2757,12 +2757,12 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -28018,7 +28018,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28038,7 +28038,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -28118,7 +28118,287 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr"/>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$2042万
+$31,027/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1817万
+$29,491/呎
+(25年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="F6" s="23" t="inlineStr">
+        <is>
+          <t>E | 570呎 (2房)
+$1725万
+$30,261/呎
+(26年-02月-03日)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>F | 581呎 (2房)
+$1391万
+$23,946/呎
+(25年-06月-27日)</t>
+        </is>
+      </c>
+      <c r="H6" s="23" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1062万
+$20,870/呎
+(25年-02月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$2010万
+$30,550/呎
+(25年-08月-21日)</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1788万
+$29,028/呎
+(25年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1701万
+$29,792/呎
+(25年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1289万
+$22,154/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="H7" s="23" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1048万
+$20,580/呎
+(25年-03月-03日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 658呎 (3房)
+$1999万
+$30,381/呎
+(25年-09月-16日)</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1778万
+$28,857/呎
+(25年-03月-28日)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1694万
+$29,674/呎
+(25年-09月-23日)</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1284万
+$22,065/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="H8" s="23" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1043万
+$20,498/呎
+(25年-02月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+$3444万
+$40,375/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1988万
+$30,161/呎
+(25年-07月-23日)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1766万
+$28,662/呎
+(25年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1796万
+$31,450/呎
+(25年-11月-19日)</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
+        <is>
+          <t>F | 505呎 (2房)
+$1279万
+$25,329/呎
+(25年-07月-11日)</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1039万
+$20,418/呎
+(25年-02月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>A | 853呎 (3房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 659呎 (3房)
+$1988万
+$30,161/呎
+(25年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 616呎 (2房)
+$1766万
+$28,662/呎
+(25年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="F10" s="23" t="inlineStr">
+        <is>
+          <t>E | 571呎 (2房)
+$1680万
+$29,425/呎
+(23年-08月-02日)</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="inlineStr">
+        <is>
+          <t>F | 582呎 (2房)
+$1279万
+$21,978/呎
+(25年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t>G | 509呎 (2房)
+$1039万
+$20,418/呎
+(25年-02月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 -
@@ -28126,288 +28406,8 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr"/>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$2042万
-$31,027/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1817万
-$29,491/呎
-(25年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>E | 570呎 (2房)
-$1725万
-$30,261/呎
-(26年-02月-03日)</t>
-        </is>
-      </c>
-      <c r="G6" s="22" t="inlineStr">
-        <is>
-          <t>F | 581呎 (2房)
-$1391万
-$23,946/呎
-(25年-06月-27日)</t>
-        </is>
-      </c>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1062万
-$20,870/呎
-(25年-02月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$2010万
-$30,550/呎
-(25年-08月-21日)</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1788万
-$29,028/呎
-(25年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1701万
-$29,792/呎
-(25年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1289万
-$22,154/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1048万
-$20,580/呎
-(25年-03月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr"/>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>C | 658呎 (3房)
-$1999万
-$30,381/呎
-(25年-09月-16日)</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1778万
-$28,857/呎
-(25年-03月-28日)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1694万
-$29,674/呎
-(25年-09月-23日)</t>
-        </is>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1284万
-$22,065/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="H8" s="22" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1043万
-$20,498/呎
-(25年-02月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
-$3444万
-$40,375/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="inlineStr"/>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1988万
-$30,161/呎
-(25年-07月-23日)</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1766万
-$28,662/呎
-(25年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1796万
-$31,450/呎
-(25年-11月-19日)</t>
-        </is>
-      </c>
-      <c r="G9" s="22" t="inlineStr">
-        <is>
-          <t>F | 505呎 (2房)
-$1279万
-$25,329/呎
-(25年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="H9" s="22" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1039万
-$20,418/呎
-(25年-02月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="21" t="inlineStr"/>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>C | 659呎 (3房)
-$1988万
-$30,161/呎
-(25年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="inlineStr">
-        <is>
-          <t>D | 616呎 (2房)
-$1766万
-$28,662/呎
-(25年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>E | 571呎 (2房)
-$1680万
-$29,425/呎
-(23年-08月-02日)</t>
-        </is>
-      </c>
-      <c r="G10" s="22" t="inlineStr">
-        <is>
-          <t>F | 582呎 (2房)
-$1279万
-$21,978/呎
-(25年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="inlineStr">
-        <is>
-          <t>G | 509呎 (2房)
-$1039万
-$20,418/呎
-(25年-02月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>A | 853呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C11" s="21" t="inlineStr"/>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $2074万
@@ -28415,7 +28415,7 @@
 (25年-07月-29日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1715万
@@ -28423,7 +28423,7 @@
 (25年-03月-26日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 571呎 (2房)
 $1667万
@@ -28431,7 +28431,7 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1269万
@@ -28439,7 +28439,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="H11" s="22" t="inlineStr">
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1031万
@@ -28454,7 +28454,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $3246万
@@ -28463,7 +28463,7 @@
         </is>
       </c>
       <c r="C12" s="21" t="inlineStr"/>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1948万
@@ -28471,7 +28471,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1689万
@@ -28479,7 +28479,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 571呎 (2房)
 $1660万
@@ -28487,7 +28487,7 @@
 (25年-12月-03日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1264万
@@ -28495,7 +28495,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1053万
@@ -28510,7 +28510,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $3030万
@@ -28519,7 +28519,7 @@
         </is>
       </c>
       <c r="C13" s="21" t="inlineStr"/>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1889万
@@ -28527,7 +28527,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1680万
@@ -28535,7 +28535,7 @@
 (25年-04月-08日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 570呎 (2房)
 $1654万
@@ -28543,7 +28543,7 @@
 (26年-02月-04日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1259万
@@ -28551,7 +28551,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H13" s="22" t="inlineStr">
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1049万
@@ -28566,7 +28566,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $3009万
@@ -28575,7 +28575,7 @@
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr"/>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1878万
@@ -28583,7 +28583,7 @@
 (25年-04月-08日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1670万
@@ -28591,7 +28591,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 571呎 (2房)
 $1647万
@@ -28599,7 +28599,7 @@
 (25年-12月-05日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1254万
@@ -28607,7 +28607,7 @@
 (25年-07月-08日)</t>
         </is>
       </c>
-      <c r="H14" s="22" t="inlineStr">
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1019万
@@ -28622,7 +28622,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $2988万
@@ -28631,7 +28631,7 @@
         </is>
       </c>
       <c r="C15" s="21" t="inlineStr"/>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1868万
@@ -28639,7 +28639,7 @@
 (25年-04月-17日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1669万
@@ -28647,7 +28647,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 571呎 (2房)
 $1640万
@@ -28655,7 +28655,7 @@
 (25年-12月-16日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1249万
@@ -28663,7 +28663,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1015万
@@ -28678,7 +28678,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $3182万
@@ -28687,7 +28687,7 @@
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr"/>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1857万
@@ -28695,7 +28695,7 @@
 (25年-04月-24日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1659万
@@ -28703,7 +28703,7 @@
 (25年-02月-10日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 570呎 (2房)
 $1634万
@@ -28711,7 +28711,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1244万
@@ -28719,7 +28719,7 @@
 (25年-07月-14日)</t>
         </is>
       </c>
-      <c r="H16" s="22" t="inlineStr">
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1011万
@@ -28734,7 +28734,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $3224万
@@ -28743,7 +28743,7 @@
         </is>
       </c>
       <c r="C17" s="21" t="inlineStr"/>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1847万
@@ -28751,7 +28751,7 @@
 (25年-05月-19日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1649万
@@ -28759,7 +28759,7 @@
 (25年-02月-27日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 570呎 (2房)
 $1627万
@@ -28767,7 +28767,7 @@
 (26年-01月-05日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1239万
@@ -28775,7 +28775,7 @@
 (25年-07月-10日)</t>
         </is>
       </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1007万
@@ -28790,7 +28790,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 $3199万
@@ -28799,7 +28799,7 @@
         </is>
       </c>
       <c r="C18" s="21" t="inlineStr"/>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1954万
@@ -28807,7 +28807,7 @@
 (25年-07月-23日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1640万
@@ -28815,7 +28815,7 @@
 (25年-02月-10日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 571呎 (2房)
 $1651万
@@ -28823,7 +28823,7 @@
 (24年-05月-13日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1234万
@@ -28831,7 +28831,7 @@
 (25年-07月-07日)</t>
         </is>
       </c>
-      <c r="H18" s="22" t="inlineStr">
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1003万
@@ -28846,7 +28846,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 招标单位
@@ -28855,7 +28855,7 @@
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr"/>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1837万
@@ -28863,7 +28863,7 @@
 (25年-07月-15日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1640万
@@ -28871,7 +28871,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 571呎 (2房)
 $1621万
@@ -28879,7 +28879,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1234万
@@ -28887,7 +28887,7 @@
 (25年-07月-03日)</t>
         </is>
       </c>
-      <c r="H19" s="22" t="inlineStr">
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $1003万
@@ -28902,7 +28902,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 招标单位
@@ -28911,7 +28911,7 @@
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr"/>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1817万
@@ -28919,7 +28919,7 @@
 (25年-08月-15日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1622万
@@ -28927,7 +28927,7 @@
 (25年-02月-24日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 570呎 (2房)
 $1615万
@@ -28935,7 +28935,7 @@
 (26年-01月-15日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1303万
@@ -28943,7 +28943,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H20" s="22" t="inlineStr">
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $995万
@@ -28958,7 +28958,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
 招标单位
@@ -28967,7 +28967,7 @@
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr"/>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 661呎 (3房)
 $1807万
@@ -28975,7 +28975,7 @@
 (25年-10月-14日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 613呎 (2房)
 $1612万
@@ -28983,7 +28983,7 @@
 (25年-03月-13日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 570呎 (2房)
 $1609万
@@ -28991,7 +28991,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1297万
@@ -28999,7 +28999,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H21" s="22" t="inlineStr">
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>G | 509呎 (2房)
 $991万
@@ -29014,7 +29014,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1428万
@@ -29022,7 +29022,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1450万
@@ -29030,7 +29030,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1571万
@@ -29038,7 +29038,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1371万
@@ -29046,7 +29046,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1540万
@@ -29054,7 +29054,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1214万
@@ -29077,7 +29077,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1356万
@@ -29085,7 +29085,7 @@
 (25年-10月-24日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1444万
@@ -29093,7 +29093,7 @@
 (23年-08月-02日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1560万
@@ -29101,7 +29101,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1362万
@@ -29109,7 +29109,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1534万
@@ -29117,7 +29117,7 @@
 (23年-08月-04日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1210万
@@ -29125,7 +29125,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="23" t="inlineStr">
         <is>
           <t>G | 403呎 (1房)
 $1080万
@@ -29140,7 +29140,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1416万
@@ -29148,7 +29148,7 @@
 (23年-08月-01日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1371万
@@ -29156,7 +29156,7 @@
 (25年-10月-28日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1549万
@@ -29164,7 +29164,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1353万
@@ -29172,7 +29172,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 567呎 (2房)
 $1556万
@@ -29180,7 +29180,7 @@
 (24年-10月-17日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1205万
@@ -29203,7 +29203,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1345万
@@ -29211,7 +29211,7 @@
 (23年-07月-31日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1366万
@@ -29219,7 +29219,7 @@
 (25年-11月-12日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1539万
@@ -29227,7 +29227,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1345万
@@ -29235,7 +29235,7 @@
 (25年-02月-04日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1522万
@@ -29243,7 +29243,7 @@
 (24年-11月-25日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1200万
@@ -29266,7 +29266,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1340万
@@ -29274,7 +29274,7 @@
 (25年-10月-30日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 518呎 (2房)
 $1360万
@@ -29282,7 +29282,7 @@
 (25年-11月-27日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1528万
@@ -29290,7 +29290,7 @@
 (25年-11月-17日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1336万
@@ -29298,7 +29298,7 @@
 (25年-02月-05日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1516万
@@ -29306,7 +29306,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1195万
@@ -29329,7 +29329,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1561万
@@ -29337,7 +29337,7 @@
 (26年-06月-24日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1360万
@@ -29345,7 +29345,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1528万
@@ -29353,7 +29353,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1370万
@@ -29361,7 +29361,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1516万
@@ -29369,7 +29369,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="G27" s="22" t="inlineStr">
+      <c r="G27" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1195万
@@ -29392,7 +29392,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1329万
@@ -29400,7 +29400,7 @@
 (25年-10月-24日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1350万
@@ -29408,7 +29408,7 @@
 (25年-11月-13日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1507万
@@ -29416,7 +29416,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1319万
@@ -29424,7 +29424,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1504万
@@ -29432,7 +29432,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="G28" s="22" t="inlineStr">
+      <c r="G28" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1186万
@@ -29455,7 +29455,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1324万
@@ -29463,7 +29463,7 @@
 (25年-10月-28日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1344万
@@ -29471,7 +29471,7 @@
 (25年-12月-05日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1496万
@@ -29479,7 +29479,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1310万
@@ -29487,7 +29487,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1498万
@@ -29495,7 +29495,7 @@
 (25年-12月-10日)</t>
         </is>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1181万
@@ -29518,7 +29518,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1318万
@@ -29526,7 +29526,7 @@
 (25年-11月-13日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1339万
@@ -29534,7 +29534,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1486万
@@ -29542,7 +29542,7 @@
 (25年-03月-21日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1302万
@@ -29550,7 +29550,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 567呎 (2房)
 $1492万
@@ -29558,7 +29558,7 @@
 (25年-12月-15日)</t>
         </is>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1176万
@@ -29581,7 +29581,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1313万
@@ -29589,7 +29589,7 @@
 (25年-10月-27日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1334万
@@ -29597,7 +29597,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1476万
@@ -29605,7 +29605,7 @@
 (25年-04月-03日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1293万
@@ -29613,7 +29613,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1486万
@@ -29621,7 +29621,7 @@
 (26年-01月-09日)</t>
         </is>
       </c>
-      <c r="G31" s="22" t="inlineStr">
+      <c r="G31" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1172万
@@ -29644,7 +29644,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1308万
@@ -29652,7 +29652,7 @@
 (25年-11月-04日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1328万
@@ -29660,7 +29660,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1465万
@@ -29668,7 +29668,7 @@
 (25年-04月-07日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1285万
@@ -29676,7 +29676,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1552万
@@ -29684,7 +29684,7 @@
 (23年-08月-10日)</t>
         </is>
       </c>
-      <c r="G32" s="22" t="inlineStr">
+      <c r="G32" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1167万
@@ -29707,7 +29707,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1303万
@@ -29715,7 +29715,7 @@
 (25年-12月-12日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1323万
@@ -29723,7 +29723,7 @@
 (25年-11月-03日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1455万
@@ -29731,7 +29731,7 @@
 (25年-04月-11日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1277万
@@ -29739,7 +29739,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1474万
@@ -29747,7 +29747,7 @@
 (25年-12月-30日)</t>
         </is>
       </c>
-      <c r="G33" s="22" t="inlineStr">
+      <c r="G33" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1162万
@@ -29770,7 +29770,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1298万
@@ -29778,7 +29778,7 @@
 (25年-11月-07日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1382万
@@ -29786,7 +29786,7 @@
 (23年-08月-10日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1445万
@@ -29794,7 +29794,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1269万
@@ -29802,7 +29802,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 567呎 (2房)
 $1603万
@@ -29810,7 +29810,7 @@
 (26年-05月-22日)</t>
         </is>
       </c>
-      <c r="G34" s="22" t="inlineStr">
+      <c r="G34" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1158万
@@ -29833,7 +29833,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1298万
@@ -29841,7 +29841,7 @@
 (25年-11月-18日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1318万
@@ -29849,7 +29849,7 @@
 (25年-12月-09日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1445万
@@ -29857,7 +29857,7 @@
 (25年-05月-20日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1269万
@@ -29865,7 +29865,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1468万
@@ -29873,7 +29873,7 @@
 (26年-01月-02日)</t>
         </is>
       </c>
-      <c r="G35" s="22" t="inlineStr">
+      <c r="G35" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1158万
@@ -29896,7 +29896,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1287万
@@ -29904,7 +29904,7 @@
 (25年-12月-04日)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1371万
@@ -29912,7 +29912,7 @@
 (23年-08月-07日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1425万
@@ -29920,7 +29920,7 @@
 (25年-04月-07日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1284万
@@ -29928,7 +29928,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 567呎 (2房)
 $1590万
@@ -29936,7 +29936,7 @@
 (26年-06月-05日)</t>
         </is>
       </c>
-      <c r="G36" s="22" t="inlineStr">
+      <c r="G36" s="23" t="inlineStr">
         <is>
           <t>F | 581呎 (2房)
 $1148万
@@ -29959,7 +29959,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>A | 517呎 (2房)
 $1282万
@@ -29967,7 +29967,7 @@
 (25年-12月-18日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 520呎 (2房)
 $1302万
@@ -29975,7 +29975,7 @@
 (25年-12月-08日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>C | 659呎 (3房)
 $1415万
@@ -29983,7 +29983,7 @@
 (25年-06月-27日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 618呎 (2房)
 $1244万
@@ -29991,7 +29991,7 @@
 (25年-02月-14日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 568呎 (2房)
 $1451万
@@ -29999,7 +29999,7 @@
 (26年-01月-08日)</t>
         </is>
       </c>
-      <c r="G37" s="22" t="inlineStr">
+      <c r="G37" s="23" t="inlineStr">
         <is>
           <t>F | 582呎 (2房)
 $1144万
@@ -30240,7 +30240,7 @@
           <t>42</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3653万
@@ -30248,7 +30248,7 @@
 (25年-11月-26日)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2219万
@@ -30256,7 +30256,7 @@
 (25年-11月-19日)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $3547万
@@ -30264,7 +30264,7 @@
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1231万
@@ -30272,7 +30272,7 @@
 (25年-03月-26日)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1092万
@@ -30280,7 +30280,7 @@
 (25年-03月-19日)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1119万
@@ -30296,7 +30296,7 @@
           <t>41</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3561万
@@ -30304,7 +30304,7 @@
 (25年-11月-26日)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2182万
@@ -30312,7 +30312,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $3033万
@@ -30320,7 +30320,7 @@
 (26年-02月-26日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1214万
@@ -30328,7 +30328,7 @@
 (25年-03月-19日)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 485呎 (2房)
 $1077万
@@ -30336,7 +30336,7 @@
 (25年-05月-16日)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1104万
@@ -30352,7 +30352,7 @@
           <t>40</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3470万
@@ -30360,7 +30360,7 @@
 (25年-11月-21日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2166万
@@ -30368,7 +30368,7 @@
 (25年-10月-16日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $3010万
@@ -30376,7 +30376,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1209万
@@ -30384,7 +30384,7 @@
 (25年-03月-19日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1073万
@@ -30392,7 +30392,7 @@
 (25年-07月-04日)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1099万
@@ -30408,7 +30408,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3378万
@@ -30416,7 +30416,7 @@
 (25年-07月-22日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2151万
@@ -30424,7 +30424,7 @@
 (25年-09月-19日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2869万
@@ -30432,7 +30432,7 @@
 (25年-06月-10日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1205万
@@ -30440,7 +30440,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1068万
@@ -30448,7 +30448,7 @@
 (25年-03月-18日)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1095万
@@ -30464,7 +30464,7 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3378万
@@ -30472,7 +30472,7 @@
 (25年-07月-28日)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2151万
@@ -30480,7 +30480,7 @@
 (25年-09月-22日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2869万
@@ -30488,7 +30488,7 @@
 (25年-07月-30日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1205万
@@ -30496,7 +30496,7 @@
 (25年-02月-18日)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1068万
@@ -30504,7 +30504,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1095万
@@ -30520,7 +30520,7 @@
           <t>37</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3295万
@@ -30528,7 +30528,7 @@
 (25年-03月-31日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2122万
@@ -30536,7 +30536,7 @@
 (25年-03月-31日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2923万
@@ -30544,7 +30544,7 @@
 (26年-02月-24日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1195万
@@ -30552,7 +30552,7 @@
 (25年-03月-04日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1060万
@@ -30560,7 +30560,7 @@
 (25年-06月-24日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1086万
@@ -30576,7 +30576,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3411万
@@ -30584,7 +30584,7 @@
 (23年-12月-21日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2138万
@@ -30592,7 +30592,7 @@
 (23年-08月-07日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2843万
@@ -30600,7 +30600,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1190万
@@ -30608,7 +30608,7 @@
 (25年-02月-14日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 485呎 (2房)
 $1056万
@@ -30616,7 +30616,7 @@
 (25年-03月-07日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1082万
@@ -30632,7 +30632,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3388万
@@ -30640,7 +30640,7 @@
 (23年-09月-19日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2085万
@@ -30648,7 +30648,7 @@
 (23年-08月-01日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2883万
@@ -30656,7 +30656,7 @@
 (26年-02月-06日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1186万
@@ -30664,7 +30664,7 @@
 (25年-03月-20日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1051万
@@ -30672,7 +30672,7 @@
 (25年-07月-02日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1077万
@@ -30688,7 +30688,7 @@
           <t>33</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3180万
@@ -30696,7 +30696,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2071万
@@ -30704,7 +30704,7 @@
 (23年-08月-02日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2863万
@@ -30712,7 +30712,7 @@
 (26年-02月-16日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1181万
@@ -30720,7 +30720,7 @@
 (25年-03月-18日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1047万
@@ -30728,7 +30728,7 @@
 (25年-06月-18日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1073万
@@ -30744,7 +30744,7 @@
           <t>32</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3157万
@@ -30752,7 +30752,7 @@
 (25年-09月-17日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2094万
@@ -30760,7 +30760,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2843万
@@ -30768,7 +30768,7 @@
 (26年-02月-23日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1176万
@@ -30776,7 +30776,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1043万
@@ -30784,7 +30784,7 @@
 (25年-02月-05日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1069万
@@ -30800,7 +30800,7 @@
           <t>31</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3134万
@@ -30808,7 +30808,7 @@
 (25年-08月-19日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2042万
@@ -30816,7 +30816,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $2998万
@@ -30824,7 +30824,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1171万
@@ -30832,7 +30832,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1039万
@@ -30840,7 +30840,7 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1065万
@@ -30856,7 +30856,7 @@
           <t>30</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3111万
@@ -30864,7 +30864,7 @@
 (25年-06月-09日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2127万
@@ -30872,7 +30872,7 @@
 (23年-07月-31日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $3080万
@@ -30880,7 +30880,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1167万
@@ -30888,7 +30888,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1035万
@@ -30896,7 +30896,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1060万
@@ -30912,7 +30912,7 @@
           <t>29</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3088万
@@ -30920,7 +30920,7 @@
 (23年-10月-20日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $2051万
@@ -30928,7 +30928,7 @@
 (23年-08月-16日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $3059万
@@ -30936,7 +30936,7 @@
 (26年-04月-10日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1162万
@@ -30944,7 +30944,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1031万
@@ -30952,7 +30952,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1056万
@@ -30968,7 +30968,7 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3065万
@@ -30976,7 +30976,7 @@
 (25年-06月-13日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $1994万
@@ -30984,7 +30984,7 @@
 (23年-08月-11日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 招标单位
@@ -30992,7 +30992,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1162万
@@ -31000,7 +31000,7 @@
 (25年-03月-26日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1031万
@@ -31008,7 +31008,7 @@
 (25年-06月-11日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1056万
@@ -31024,7 +31024,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3088万
@@ -31032,7 +31032,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $1942万
@@ -31040,7 +31040,7 @@
 (25年-04月-08日)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 招标单位
@@ -31048,7 +31048,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1153万
@@ -31056,7 +31056,7 @@
 (25年-04月-08日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1022万
@@ -31064,7 +31064,7 @@
 (25年-06月-09日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1048万
@@ -31080,7 +31080,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 915呎 (3房)
 $3065万
@@ -31088,7 +31088,7 @@
 (25年-10月-09日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 678呎 (2房)
 $1904万
@@ -31096,7 +31096,7 @@
 (25年-04月-10日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 861呎 (3房)
 $3014万
@@ -31104,7 +31104,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1148万
@@ -31112,7 +31112,7 @@
 (25年-03月-19日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 486呎 (2房)
 $1018万
@@ -31120,7 +31120,7 @@
 (25年-04月-28日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 505呎 (2房)
 $1044万
@@ -31136,7 +31136,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $3027万
@@ -31144,7 +31144,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1882万
@@ -31152,7 +31152,7 @@
 (25年-10月-30日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1452万
@@ -31160,7 +31160,7 @@
 (25年-03月-26日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1144万
@@ -31168,7 +31168,7 @@
 (25年-02月-26日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $1014万
@@ -31199,7 +31199,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $3044万
@@ -31207,7 +31207,7 @@
 (26年-03月-11日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1907万
@@ -31215,7 +31215,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1445万
@@ -31223,7 +31223,7 @@
 (25年-04月-01日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1139万
@@ -31231,7 +31231,7 @@
 (25年-02月-20日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $1010万
@@ -31262,7 +31262,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2932万
@@ -31270,7 +31270,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1955万
@@ -31278,7 +31278,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1438万
@@ -31286,7 +31286,7 @@
 (25年-05月-12日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1135万
@@ -31294,7 +31294,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $1006万
@@ -31325,7 +31325,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $3053万
@@ -31333,7 +31333,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1854万
@@ -31341,7 +31341,7 @@
 (25年-11月-03日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1431万
@@ -31349,7 +31349,7 @@
 (25年-05月-23日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1130万
@@ -31357,7 +31357,7 @@
 (25年-02月-19日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $1002万
@@ -31365,7 +31365,7 @@
 (25年-03月-04日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 394呎 (1房)
 $1056万
@@ -31388,7 +31388,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2891万
@@ -31396,7 +31396,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1879万
@@ -31404,7 +31404,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1423万
@@ -31412,7 +31412,7 @@
 (25年-05月-08日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1126万
@@ -31420,7 +31420,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $998万
@@ -31451,7 +31451,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="B27" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2891万
@@ -31459,7 +31459,7 @@
 (23年-08月-04日)</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1845万
@@ -31467,7 +31467,7 @@
 (25年-11月-11日)</t>
         </is>
       </c>
-      <c r="D27" s="22" t="inlineStr">
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1423万
@@ -31475,7 +31475,7 @@
 (25年-05月-23日)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1126万
@@ -31483,7 +31483,7 @@
 (25年-02月-05日)</t>
         </is>
       </c>
-      <c r="F27" s="22" t="inlineStr">
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $998万
@@ -31514,7 +31514,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B28" s="22" t="inlineStr">
+      <c r="B28" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2903万
@@ -31522,7 +31522,7 @@
 (23年-08月-11日)</t>
         </is>
       </c>
-      <c r="C28" s="22" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1827万
@@ -31530,7 +31530,7 @@
 (23年-08月-11日)</t>
         </is>
       </c>
-      <c r="D28" s="22" t="inlineStr">
+      <c r="D28" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1409万
@@ -31538,7 +31538,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1117万
@@ -31546,7 +31546,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="F28" s="22" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $990万
@@ -31577,7 +31577,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2883万
@@ -31585,7 +31585,7 @@
 (23年-08月-07日)</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1818万
@@ -31593,7 +31593,7 @@
 (23年-08月-02日)</t>
         </is>
       </c>
-      <c r="D29" s="22" t="inlineStr">
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1402万
@@ -31601,7 +31601,7 @@
 (25年-05月-19日)</t>
         </is>
       </c>
-      <c r="E29" s="22" t="inlineStr">
+      <c r="E29" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1112万
@@ -31609,7 +31609,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="F29" s="22" t="inlineStr">
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $986万
@@ -31640,7 +31640,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $3288万
@@ -31648,7 +31648,7 @@
 (26年-06月-26日)</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1897万
@@ -31656,7 +31656,7 @@
 (23年-10月-10日)</t>
         </is>
       </c>
-      <c r="D30" s="22" t="inlineStr">
+      <c r="D30" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1395万
@@ -31664,7 +31664,7 @@
 (25年-04月-29日)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1108万
@@ -31672,7 +31672,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="F30" s="22" t="inlineStr">
+      <c r="F30" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $982万
@@ -31703,7 +31703,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2928万
@@ -31711,7 +31711,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1888万
@@ -31719,7 +31719,7 @@
 (23年-08月-03日)</t>
         </is>
       </c>
-      <c r="D31" s="22" t="inlineStr">
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1388万
@@ -31727,7 +31727,7 @@
 (25年-05月-28日)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1103万
@@ -31735,7 +31735,7 @@
 (25年-02月-11日)</t>
         </is>
       </c>
-      <c r="F31" s="22" t="inlineStr">
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $978万
@@ -31766,7 +31766,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2908万
@@ -31774,7 +31774,7 @@
 (23年-08月-04日)</t>
         </is>
       </c>
-      <c r="C32" s="22" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1878万
@@ -31782,7 +31782,7 @@
 (23年-08月-10日)</t>
         </is>
       </c>
-      <c r="D32" s="22" t="inlineStr">
+      <c r="D32" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1381万
@@ -31790,7 +31790,7 @@
 (25年-06月-10日)</t>
         </is>
       </c>
-      <c r="E32" s="22" t="inlineStr">
+      <c r="E32" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1099万
@@ -31798,7 +31798,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F32" s="22" t="inlineStr">
+      <c r="F32" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $974万
@@ -31829,7 +31829,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="22" t="inlineStr">
+      <c r="B33" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2753万
@@ -31837,7 +31837,7 @@
 (25年-10月-03日)</t>
         </is>
       </c>
-      <c r="C33" s="22" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1782万
@@ -31845,7 +31845,7 @@
 (25年-11月-19日)</t>
         </is>
       </c>
-      <c r="D33" s="22" t="inlineStr">
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1375万
@@ -31853,7 +31853,7 @@
 (25年-06月-20日)</t>
         </is>
       </c>
-      <c r="E33" s="22" t="inlineStr">
+      <c r="E33" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1094万
@@ -31861,7 +31861,7 @@
 (25年-02月-12日)</t>
         </is>
       </c>
-      <c r="F33" s="22" t="inlineStr">
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $971万
@@ -31892,7 +31892,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
+      <c r="B34" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2868万
@@ -31900,7 +31900,7 @@
 (23年-08月-09日)</t>
         </is>
       </c>
-      <c r="C34" s="22" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1860万
@@ -31908,7 +31908,7 @@
 (23年-08月-08日)</t>
         </is>
       </c>
-      <c r="D34" s="22" t="inlineStr">
+      <c r="D34" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1368万
@@ -31916,7 +31916,7 @@
 (25年-04月-03日)</t>
         </is>
       </c>
-      <c r="E34" s="22" t="inlineStr">
+      <c r="E34" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1090万
@@ -31924,7 +31924,7 @@
 (25年-02月-06日)</t>
         </is>
       </c>
-      <c r="F34" s="22" t="inlineStr">
+      <c r="F34" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $967万
@@ -31955,7 +31955,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2762万
@@ -31963,7 +31963,7 @@
 (25年-12月-30日)</t>
         </is>
       </c>
-      <c r="C35" s="22" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1805万
@@ -31971,7 +31971,7 @@
 (24年-06月-03日)</t>
         </is>
       </c>
-      <c r="D35" s="22" t="inlineStr">
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1368万
@@ -31979,7 +31979,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="E35" s="22" t="inlineStr">
+      <c r="E35" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1090万
@@ -31987,7 +31987,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F35" s="22" t="inlineStr">
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $967万
@@ -32018,7 +32018,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2762万
@@ -32026,7 +32026,7 @@
 (26年-03月-10日)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1788万
@@ -32034,7 +32034,7 @@
 (24年-06月-05日)</t>
         </is>
       </c>
-      <c r="D36" s="22" t="inlineStr">
+      <c r="D36" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1354万
@@ -32042,7 +32042,7 @@
 (25年-06月-23日)</t>
         </is>
       </c>
-      <c r="E36" s="22" t="inlineStr">
+      <c r="E36" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1082万
@@ -32050,7 +32050,7 @@
 (25年-02月-07日)</t>
         </is>
       </c>
-      <c r="F36" s="22" t="inlineStr">
+      <c r="F36" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $959万
@@ -32081,7 +32081,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
+      <c r="B37" s="23" t="inlineStr">
         <is>
           <t>A | 914呎 (3房)
 $2678万
@@ -32089,7 +32089,7 @@
 (25年-08月-22日)</t>
         </is>
       </c>
-      <c r="C37" s="22" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 680呎 (2房)
 $1747万
@@ -32097,7 +32097,7 @@
 (25年-11月-26日)</t>
         </is>
       </c>
-      <c r="D37" s="22" t="inlineStr">
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>C | 629呎 (2房)
 $1347万
@@ -32105,7 +32105,7 @@
 (25年-06月-25日)</t>
         </is>
       </c>
-      <c r="E37" s="22" t="inlineStr">
+      <c r="E37" s="23" t="inlineStr">
         <is>
           <t>D | 535呎 (2房)
 $1077万
@@ -32113,7 +32113,7 @@
 (25年-02月-13日)</t>
         </is>
       </c>
-      <c r="F37" s="22" t="inlineStr">
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>E | 488呎 (2房)
 $955万

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -2747,38 +2747,30 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>35474000</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>41587</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K34" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K34" s="5" t="n">
+        <v>35474000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>41587</v>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
@@ -2787,7 +2779,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28018,7 +28010,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28028,7 +28020,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>186</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -28342,12 +28334,12 @@
           <t>38</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
-招标单位
--
-(在售)</t>
+$3547万
+$41,587/呎
+(26年-08月-17日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -5913,7 +5913,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>16209800</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>28388</v>
+        <v>28438</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5940,7 +5940,7 @@
         <v>16209800</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>28388</v>
+        <v>28438</v>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
@@ -28865,9 +28865,9 @@
       </c>
       <c r="F19" s="23" t="inlineStr">
         <is>
-          <t>E | 571呎 (2房)
+          <t>E | 570呎 (2房)
 $1621万
-$28,388/呎
+$28,438/呎
 (26年-01月-09日)</t>
         </is>
       </c>

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>16944000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>29674</v>
+        <v>29726</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1832,7 +1832,7 @@
         <v>16944000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>29674</v>
+        <v>29726</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -28249,9 +28249,9 @@
       </c>
       <c r="F8" s="23" t="inlineStr">
         <is>
-          <t>E | 571呎 (2房)
+          <t>E | 570呎 (2房)
 $1694万
-$29,674/呎
+$29,726/呎
 (25年-09月-23日)</t>
         </is>
       </c>

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H88" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J88" s="3" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M88" s="3" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6483,7 +6483,7 @@
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G94" s="3" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="H94" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J94" s="3" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M94" s="3" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="N94" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6863,7 +6863,7 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>待售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="H100" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="I100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="J100" s="3" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M100" s="3" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28010,7 +28010,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28030,7 +28030,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -28339,7 +28339,7 @@
           <t>A | 853呎 (3房)
 $3547万
 $41,587/呎
-(26年-08月-17日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="C10" s="21" t="inlineStr"/>
@@ -28838,12 +28838,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C19" s="21" t="inlineStr"/>
@@ -28894,12 +28894,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C20" s="21" t="inlineStr"/>
@@ -28950,12 +28950,12 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 853呎 (3房)
-招标单位
 -
-(在售)</t>
+-
+(待售)</t>
         </is>
       </c>
       <c r="C21" s="21" t="inlineStr"/>

--- a/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-海盈山第4A期/海盈山第4A期_销控明细表.xlsx
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="E74" s="4" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>16494700</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>26908</v>
+        <v>26864</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>16494700</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>26908</v>
+        <v>26864</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -28745,9 +28745,9 @@
       </c>
       <c r="E17" s="23" t="inlineStr">
         <is>
-          <t>D | 613呎 (2房)
+          <t>D | 614呎 (2房)
 $1649万
-$26,908/呎
+$26,864/呎
 (25年-02月-27日)</t>
         </is>
       </c>
